--- a/docs/sales-kit/market_cairo.xlsx
+++ b/docs/sales-kit/market_cairo.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Call list" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sources" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Overview" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sources" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Call list'!$A$1:$O$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Call list'!$A$4:$N$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,15 +32,45 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="000D2B24"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="005B7169"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B6B5C"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -56,8 +87,18 @@
         <fgColor rgb="00FDECEA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F0E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,29 +106,83 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,1197 +548,2485 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Who to call, in the order to call them</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Grouped by district first, then by score. Five clinics in one district in an afternoon beats five scattered across Cairo - vets in a district talk to each other, and that is the whole mechanism. Green = 8+, worth the drive. Red = no number yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>Cohort</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Clinic</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>الاسم</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Governorate</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>District</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Signals</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>What they run</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Already using</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Reachable</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Last contact</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Next action</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>When</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="n">
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>American Vet Center</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>2 branches</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>Open 24/7. Two cities - Cairo and Alexandria - so multi-governorate. PHONE NOT YET FOUND.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>Open 24/7. Two GOVERNORATES - Cairo and Alexandria - so a multi-site buyer. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>British Animal Hospital</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>hospital</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Hospital by name. Details not yet confirmed.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="n">
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Dr Men3am Pet Hospital</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>مستشفى د. منعم</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>hospital</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>VetICare</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n"/>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>NAMED AS A VETICARE CUSTOMER in docs/market/01_COMPETITORS.md. Already pays for vet software.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="n">
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>name only</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>NAMED VETICARE CUSTOMER. A HOSPITAL already paying a competitor - the highest-value switch target on this list once you can reach them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Almotawakkel Pet Center</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>مركز المتوكل</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>VetICare</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>NAMED AS A VETICARE CUSTOMER in docs/market/01_COMPETITORS.md. Already pays for vet software.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="n">
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>name only</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>NAMED VETICARE CUSTOMER. Already pays for vet software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Pets Zone</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>VetICare</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>NAMED AS A VETICARE CUSTOMER in docs/market/01_COMPETITORS.md. Already pays for vet software.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="4" t="n">
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>name only</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>NAMED VETICARE CUSTOMER from the competitor research. Already pays for vet software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Biofy Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>عيادة بيوفي</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Badr City</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>Also does poultry and farm supervision - a different business shape. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Petzone Clinics - Heliopolis</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Heliopolis</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>01090390071</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>3 branches · grooming · boarding · pharmacy · lab</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>Branch of Petzone. Same decision maker as the New Cairo record.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="n">
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>BRANCH of Petzone - same decision maker as the New Cairo record. Do not pitch twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Golf Veterinary Clinic Heliopolis</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>عيادة الجولف البيطرية</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Heliopolis</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>Pharmacy and specialist vets advertised. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Heliopolis Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>العيادة البيطرية بمصر الجديدة</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Heliopolis</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>Pharmacy advertised. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Pet Vet Clinic</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>عيادة بيت فيت البيطرية</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Heliopolis</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Pets Galaxy</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Heliopolis</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>shop</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="7" t="inlineStr">
         <is>
           <t>PHONE NOT YET FOUND.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="n">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Pets Home</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Heliopolis</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>shop</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="7" t="inlineStr">
         <is>
           <t>PHONE NOT YET FOUND.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="2" t="n">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Pets Valley</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Heliopolis</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>shop</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="7" t="inlineStr">
         <is>
           <t>Name suggests retail alongside the clinic. PHONE NOT YET FOUND.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="4" t="n">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Vital Pets Center</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>مركز فيتال بيتس</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Heliopolis</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>Pharmacy advertised. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Dr Birjy Yaqoub Clinic</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>عيادة دكتور بيرجي يعقوب</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Heliopolis</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Named after the vet - the decision maker is on the sign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>Sheraton Vet Clinic</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr"/>
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>Heliopolis</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>01126782224</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>Three lines listed: 01126782224 / 01144000034 / 01092449442.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="4" t="n">
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>01126782224</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr"/>
+      <c r="I20" s="15" t="inlineStr"/>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t>Three lines: 01126782224 / 01144000034 / 01092449442 - a three-line clinic is usually a busy one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>International Veterinary Hospital</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>المستشفى البيطري الدولى</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Katameya</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>Hospital. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Dr Sameh Nabil Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>عيادة د. سامح نبيل البيطرية</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Maadi</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>0225168672</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr"/>
+      <c r="H22" s="17" t="inlineStr"/>
+      <c r="I22" s="15" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t>Landline. Named after the vet - decision maker on the sign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Golf Veterinary Clinic Maadi</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>عيادة الجولف البيطرية</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Maadi</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>01005111956</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>01005111956</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr"/>
+      <c r="I23" s="15" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="17" t="inlineStr"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>I-Vet Clinic</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr"/>
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Maadi</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>01006895894</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr"/>
+      <c r="H24" s="17" t="inlineStr"/>
+      <c r="I24" s="15" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K24" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="17" t="inlineStr">
         <is>
           <t>Second line 0227538802.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="4" t="n">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>Maadi Veterinary Clinic</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>العيادة البيطرية بالمعادي</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Maadi</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>01005058650</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="4" t="n">
+      <c r="G25" s="15" t="inlineStr"/>
+      <c r="H25" s="17" t="inlineStr"/>
+      <c r="I25" s="15" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K25" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L25" s="15" t="n"/>
+      <c r="M25" s="15" t="n"/>
+      <c r="N25" s="17" t="inlineStr"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>Mojo Veterinary Care</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr"/>
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Maadi</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>01003454200</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>01003454200</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="H26" s="17" t="inlineStr"/>
+      <c r="I26" s="15" t="inlineStr">
         <is>
           <t>VetICare</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>24/7 emergency. NAMED AS A VETICARE CUSTOMER in docs/market/01_COMPETITORS.md - they already pay for vet software.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="4" t="n">
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K26" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L26" s="15" t="n"/>
+      <c r="M26" s="15" t="n"/>
+      <c r="N26" s="17" t="inlineStr">
+        <is>
+          <t>24/7 emergency. NAMED VETICARE CUSTOMER - they already pay for vet software, so willingness to pay is proven and a contract is in the way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Pawsitive Veterinary Clinic</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Maadi</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>01067190492</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="G27" s="16" t="inlineStr">
         <is>
           <t>01067190492</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>Second line 01017346255. Active on Instagram.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="n">
+      <c r="H27" s="17" t="inlineStr"/>
+      <c r="I27" s="15" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L27" s="15" t="n"/>
+      <c r="M27" s="15" t="n"/>
+      <c r="N27" s="17" t="inlineStr">
+        <is>
+          <t>Second line 01017346255. Active on Instagram - reachable by DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Animalz</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>أنيمالز</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Nasr City</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>pharmacy · shop</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>Pharmacy AND pet supplies - two signals. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Lovely Pets Clinic</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>عيادة لavely بيتس البيطرية</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Nasr City</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>Pharmacy advertised. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Pet Hotel Nasr City</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>فندق استضافة قطط وكلاب</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Nasr City</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>boarding</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>BOARDING-LED business with veterinary supervision. Different shape from a clinic - boarding is a strong Aleefy signal. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Happy Pets</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>هابي بيتس</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Nasr City</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>PWC Veterinary Center</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>مركز بي دبليو سي البيطري</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Nasr City</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Pet Care Center</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>Nasr City</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="6" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="7" t="inlineStr">
         <is>
           <t>PHONE NOT YET FOUND.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="2" t="n">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Pets Care Clinic</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>عيادة بيتس كير البيطرية</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>Nasr City</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
+      <c r="N34" s="7" t="inlineStr">
         <is>
           <t>PHONE NOT YET FOUND.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="n">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Pets Steps</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>Nasr City</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
+      <c r="N35" s="7" t="inlineStr">
         <is>
           <t>PHONE NOT YET FOUND.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="4" t="n">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>VIPets Clinic</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>عيادة في أي بيتس البيطرية</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Nasr City</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Dr Paws Animal Hospital</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr"/>
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>New Cairo</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>01117873666</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>01117873666</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>3 branches · hospital · grooming · boarding · lab</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="n"/>
+      <c r="M37" s="10" t="n"/>
+      <c r="N37" s="12" t="inlineStr">
         <is>
           <t>3 branches: New Cairo, Sheikh Zayed, New Giza. 24/7 emergency, X-ray + ultrasound, hospitalisation, home visits, exotics.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="4" t="n">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Petzone Clinics</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr"/>
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>New Cairo</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>01211288882</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr"/>
+      <c r="H38" s="12" t="inlineStr">
         <is>
           <t>3 branches · grooming · boarding · pharmacy · lab</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>3 branches: New Cairo, Mohandessin, Heliopolis. Specialists in ortho, cardio, derm, dentistry, gynae, ophthalmology, oncology. info@petzoneclinics.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="4" t="n">
+      <c r="I38" s="10" t="inlineStr"/>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="12" t="inlineStr">
+        <is>
+          <t>HEAD OFFICE of a 3-branch group. Specialists in ortho, cardio, derm, dentistry, gynae, ophthalmology, oncology. info@petzoneclinics.com. Landline 02 25606590.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>VENN Animal Hospital</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr"/>
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>New Cairo</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>01080000657</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>01080000657</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>hospital · grooming · boarding · lab</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="12" t="inlineStr">
         <is>
           <t>24/7. Markets AI diagnostics and home visits.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="2" t="n">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Pet Cure Veterinary Clinics</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>New Cairo</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>3 branches · grooming</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
+      <c r="N40" s="7" t="inlineStr">
         <is>
           <t>3 locations: Al Rehab, Madinaty, New Cairo. House calls, dental, dog licences and certificates. PHONE NOT YET FOUND.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="4" t="n">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Lotus Veterinary Hospital</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>مستشفى اللوتس البيطري</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>New Cairo</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>Hospital. Surgery and vaccinations advertised. PHONE NOT YET FOUND - Facebook page is the route in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Pet Hotel New Cairo</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>فندق استضافة قطط وكلاب</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>New Cairo</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>boarding</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>BOARDING-LED with air conditioning and therapeutic boarding. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Pet Palace</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>بيت بالاس</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>New Cairo</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>Name and location suggest retail alongside the clinic. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Pet Republic</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>بت ريبابلك</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>New Cairo</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>Pet supplies plus veterinary services - retail signal. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Vetology Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>فيتولوجي البيطرية</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>New Cairo</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>Surgery advertised. PHONE NOT YET FOUND - Facebook is the route in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Pharma Vet</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>فارما فيت</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>New Maadi</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>0227038751</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr"/>
+      <c r="H46" s="17" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr"/>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K46" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L46" s="15" t="n"/>
+      <c r="M46" s="15" t="n"/>
+      <c r="N46" s="17" t="inlineStr">
+        <is>
+          <t>Name is pharmacy-led. Second line 0227043664.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>New Maadi Vet Clinic</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr"/>
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>New Maadi</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>01222198733</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="2" t="n">
+      <c r="G47" s="15" t="inlineStr"/>
+      <c r="H47" s="17" t="inlineStr"/>
+      <c r="I47" s="15" t="inlineStr"/>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K47" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L47" s="15" t="n"/>
+      <c r="M47" s="15" t="n"/>
+      <c r="N47" s="17" t="inlineStr"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>New York Veterinary Clinics</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>عيادات نيويورك البيطرية</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>New Maadi</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>01101160688</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>01101160688</t>
+        </is>
+      </c>
+      <c r="H48" s="17" t="inlineStr"/>
+      <c r="I48" s="15" t="inlineStr"/>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K48" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L48" s="15" t="n"/>
+      <c r="M48" s="15" t="n"/>
+      <c r="N48" s="17" t="inlineStr">
+        <is>
+          <t>Plural name - possible multi-site. Worth asking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Paws &amp; Claws Vet Clinic</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>New Maadi</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="3" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="n"/>
+      <c r="M49" s="6" t="n"/>
+      <c r="N49" s="7" t="inlineStr">
         <is>
           <t>PHONE NOT YET FOUND.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B25" s="4" t="n">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Harmony Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>عيادة هارموني البيطرية</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Nozha</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>grooming</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="n"/>
+      <c r="M50" s="6" t="n"/>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>Grooming and dental advertised. PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>El-Nozha Veterinary</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>النزهة البيطرية</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>Nozha</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Paws and Claws Veterinary Clinic - Obour</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>عيادة بوز أند كلوز</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>Obour</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="n"/>
+      <c r="M52" s="6" t="n"/>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Prime Vet Clinic</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>برايم فيت</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Shorouk</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>PHONE NOT YET FOUND.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Nile Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D54" s="15" t="inlineStr">
+        <is>
+          <t>عيادة النيل البيطرية</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>Zahraa El Maadi</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>0225199849</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="inlineStr"/>
+      <c r="H54" s="17" t="inlineStr"/>
+      <c r="I54" s="15" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L54" s="15" t="n"/>
+      <c r="M54" s="15" t="n"/>
+      <c r="N54" s="17" t="inlineStr">
+        <is>
+          <t>Landline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>Petzone Clinics - Mohandessin</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Giza</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr"/>
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>Mohandessin</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>01099975999</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="G55" s="10" t="inlineStr"/>
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>3 branches · grooming · boarding · pharmacy · lab</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>Branch of Petzone. Same decision maker as the New Cairo record.</t>
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="12" t="inlineStr">
+        <is>
+          <t>BRANCH of Petzone - same decision maker as the New Cairo record. Do not pitch twice.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O25"/>
+  <autoFilter ref="A4:N55"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1654,440 +3037,1271 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The market, from above</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>Clinics mapped</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="n">
+        <v>51</v>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>every one carries the URL its facts came from</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>Callable today</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>a phone or WhatsApp number is on file</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Need a number</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>an address or Facebook page but no phone - minutes each to find</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>Score 8 or more</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>multi-branch or full-service: the clinics Aleefy's breadth is FOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Already on a competitor</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>willingness to pay is proven, and a contract is in the way</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>By district</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>District</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>Clinics</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Callable</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Heliopolis</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Nasr City</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>New Cairo</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Maadi</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>(not recorded)</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>New Maadi</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Nozha</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Badr City</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Katameya</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Obour</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Shorouk</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Zahraa El Maadi</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Mohandessin</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Work one district at a time. Density is the mechanism - the goal is a vet saying 'I know several clinics using it', which never happens from one clinic per area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A25:C26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Where every record came from</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>A market database nobody can audit is a list of rumours, and the first wrong phone number destroys trust in all of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Clinic</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>American Vet Center</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>https://www.americanvetcenter.com/</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>British Animal Hospital</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>search result</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>http://britishanimalhospital.com/</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>Dr Men3am Pet Hospital</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>competitor research</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>https://veticareapp.com/</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Almotawakkel Pet Center</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>competitor research</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>https://veticareapp.com/</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Pets Zone</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>competitor research</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>https://veticareapp.com/</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Biofy Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Petzone Clinics - Heliopolis</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>https://petzoneclinics.com/</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Golf Veterinary Clinic Heliopolis</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>Heliopolis Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Pet Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>Pets Galaxy</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>Pets Home</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>Pets Valley</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Vital Pets Center</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Dr Birjy Yaqoub Clinic</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Sheraton Vet Clinic</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>International Veterinary Hospital</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Dr Sameh Nabil Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Arabic directory</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Golf Veterinary Clinic Maadi</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Arabic directory</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>I-Vet Clinic</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Maadi Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>https://eg.daleel.waseet.net/en/cairo/</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Mojo Veterinary Care</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>competitor research</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>https://veticareapp.com/</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Pawsitive Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Animalz</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Lovely Pets Clinic</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Pet Hotel Nasr City</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Happy Pets</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>PWC Veterinary Center</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>Pet Care Center</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Pets Care Clinic</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Pets Steps</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Pets Steps</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>VIPets Clinic</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Dr Paws Animal Hospital</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>vendor site</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>https://drpaws.com.eg/en/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Petzone Clinics</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>vendor site</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>https://petzoneclinics.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>VENN Animal Hospital</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>vendor site</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>https://vennvet.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>Pet Cure Veterinary Clinics</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>vendor site</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>https://petcureclinics.com/about-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>Lotus Veterinary Hospital</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>Pet Hotel New Cairo</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>Pet Palace</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Pet Republic</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>Vetology Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Pharma Vet</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Arabic directory</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>New Maadi Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Dr Paws Animal Hospital</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>New York Veterinary Clinics</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Arabic directory</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>Paws &amp; Claws Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>directory</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Harmony Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>El-Nozha Veterinary</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>Paws and Claws Veterinary Clinic - Obour</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>Prime Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>evcindex directory</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>Nile Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Arabic directory</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Petzone Clinics - Mohandessin</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>https://drpaws.com.eg/en/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Petzone Clinics</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>vendor site</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
         <is>
           <t>https://petzoneclinics.com/</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>VENN Animal Hospital</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>vendor site</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>https://vennvet.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Pet Cure Veterinary Clinics</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>vendor site</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>https://petcureclinics.com/about-us</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>New Maadi Vet Clinic</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>directory</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Paws &amp; Claws Vet Clinic</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>directory</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Petzone Clinics - Mohandessin</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>vendor site</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>https://petzoneclinics.com/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/sales-kit/market_cairo.xlsx
+++ b/docs/sales-kit/market_cairo.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Call list'!$A$4:$N$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Call list'!$A$4:$N$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -70,7 +70,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +95,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF6E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -124,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,6 +178,21 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -548,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -655,7 +675,7 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>3</v>
@@ -695,7 +715,7 @@
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>2</v>
@@ -735,7 +755,7 @@
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>2</v>
@@ -867,7 +887,7 @@
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>0</v>
@@ -1055,7 +1075,7 @@
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>2</v>
@@ -1191,7 +1211,7 @@
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>2</v>
@@ -1283,7 +1303,7 @@
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>0</v>
@@ -1423,7 +1443,7 @@
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="13" t="n">
         <v>0</v>
@@ -1471,7 +1491,7 @@
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" s="13" t="n">
         <v>0</v>
@@ -1519,7 +1539,7 @@
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="13" t="n">
         <v>0</v>
@@ -1563,7 +1583,7 @@
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" s="13" t="n">
         <v>0</v>
@@ -1659,7 +1679,7 @@
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" s="13" t="n">
         <v>0</v>
@@ -1755,7 +1775,7 @@
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" s="4" t="n">
         <v>2</v>
@@ -1851,7 +1871,7 @@
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" s="4" t="n">
         <v>0</v>
@@ -1895,7 +1915,7 @@
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" s="4" t="n">
         <v>0</v>
@@ -1939,7 +1959,7 @@
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" s="4" t="n">
         <v>0</v>
@@ -1979,7 +1999,7 @@
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B34" s="4" t="n">
         <v>0</v>
@@ -2023,7 +2043,7 @@
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B35" s="4" t="n">
         <v>0</v>
@@ -2259,7 +2279,7 @@
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" s="4" t="n">
         <v>5</v>
@@ -2323,7 +2343,7 @@
           <t>New Cairo</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="n"/>
       <c r="G41" s="6" t="inlineStr"/>
       <c r="H41" s="7" t="inlineStr">
         <is>
@@ -2495,7 +2515,7 @@
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B45" s="4" t="n">
         <v>0</v>
@@ -2591,7 +2611,7 @@
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" s="13" t="n">
         <v>0</v>
@@ -2631,7 +2651,7 @@
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" s="13" t="n">
         <v>0</v>
@@ -2723,7 +2743,7 @@
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" s="4" t="n">
         <v>2</v>
@@ -2859,7 +2879,7 @@
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" s="4" t="n">
         <v>0</v>
@@ -2950,55 +2970,3263 @@
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="8" t="n">
+      <c r="A55" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B55" s="8" t="n">
+      <c r="B55" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>Pets Mall Hospital</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr"/>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>01033076100</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="inlineStr">
+        <is>
+          <t>01033076100</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>hospital · shop</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr"/>
+      <c r="J55" s="18" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K55" s="20" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="n"/>
+      <c r="M55" s="20" t="n"/>
+      <c r="N55" s="22" t="inlineStr">
+        <is>
+          <t>Hospital, and the name says retail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Almedan Pet Hospital October</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="inlineStr"/>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>01140891077</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>01140891077</t>
+        </is>
+      </c>
+      <c r="H56" s="17" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr"/>
+      <c r="J56" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K56" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L56" s="15" t="n"/>
+      <c r="M56" s="15" t="n"/>
+      <c r="N56" s="17" t="inlineStr">
+        <is>
+          <t>Hospital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Catdog Hospital</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr"/>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>01032288638</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>01032288638</t>
+        </is>
+      </c>
+      <c r="H57" s="17" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="I57" s="15" t="inlineStr"/>
+      <c r="J57" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K57" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L57" s="15" t="n"/>
+      <c r="M57" s="15" t="n"/>
+      <c r="N57" s="17" t="inlineStr">
+        <is>
+          <t>Hospital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Fardous Pets Clinics</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr"/>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
+        <is>
+          <t>01066116129</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>01066116129</t>
+        </is>
+      </c>
+      <c r="H58" s="17" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr"/>
+      <c r="J58" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K58" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L58" s="15" t="n"/>
+      <c r="M58" s="15" t="n"/>
+      <c r="N58" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01017476390. Pet shop alongside the clinic. Two lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>Pets Place Clinic</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr"/>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>01066536769</t>
+        </is>
+      </c>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>01066536769</t>
+        </is>
+      </c>
+      <c r="H59" s="17" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="inlineStr"/>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K59" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L59" s="15" t="n"/>
+      <c r="M59" s="15" t="n"/>
+      <c r="N59" s="17" t="inlineStr">
+        <is>
+          <t>Pet shop alongside the clinic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Pets Planet Clinic</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr"/>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>01009782040</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>01009782040</t>
+        </is>
+      </c>
+      <c r="H60" s="17" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr"/>
+      <c r="J60" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K60" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L60" s="15" t="n"/>
+      <c r="M60" s="15" t="n"/>
+      <c r="N60" s="17" t="inlineStr">
+        <is>
+          <t>Pet shop alongside the clinic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Very Important Pets</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr"/>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>01207100037</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>01207100037</t>
+        </is>
+      </c>
+      <c r="H61" s="17" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I61" s="15" t="inlineStr"/>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K61" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L61" s="15" t="n"/>
+      <c r="M61" s="15" t="n"/>
+      <c r="N61" s="17" t="inlineStr">
+        <is>
+          <t>Pharmacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Vet4u</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr"/>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>01030230303</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>01030230303</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="inlineStr"/>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K62" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L62" s="15" t="n"/>
+      <c r="M62" s="15" t="n"/>
+      <c r="N62" s="17" t="inlineStr">
+        <is>
+          <t>Pharmacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Veterinary Pharmacy October</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr"/>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>01001492834</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>01001492834</t>
+        </is>
+      </c>
+      <c r="H63" s="17" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I63" s="15" t="inlineStr"/>
+      <c r="J63" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K63" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L63" s="15" t="n"/>
+      <c r="M63" s="15" t="n"/>
+      <c r="N63" s="17" t="inlineStr">
+        <is>
+          <t>Pharmacy-led.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B64" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Vito Vet</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr"/>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>01066649424</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>01066649424</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I64" s="15" t="inlineStr"/>
+      <c r="J64" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K64" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L64" s="15" t="n"/>
+      <c r="M64" s="15" t="n"/>
+      <c r="N64" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01154941444. Pharmacy, two lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>3naya Pet Clinic</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr"/>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>01062698267</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>01062698267</t>
+        </is>
+      </c>
+      <c r="H65" s="17" t="inlineStr"/>
+      <c r="I65" s="15" t="inlineStr"/>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K65" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L65" s="15" t="n"/>
+      <c r="M65" s="15" t="n"/>
+      <c r="N65" s="17" t="inlineStr"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>6 October Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr"/>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>01001979263</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>01001979263</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr"/>
+      <c r="I66" s="15" t="inlineStr"/>
+      <c r="J66" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K66" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L66" s="15" t="n"/>
+      <c r="M66" s="15" t="n"/>
+      <c r="N66" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01115688873.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Al-Siyaha Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr"/>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>01024779743</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>01024779743</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr"/>
+      <c r="I67" s="15" t="inlineStr"/>
+      <c r="J67" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K67" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L67" s="15" t="n"/>
+      <c r="M67" s="15" t="n"/>
+      <c r="N67" s="17" t="inlineStr"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Aleefy Veterinary Center</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr"/>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>01099776287</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>01099776287</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr"/>
+      <c r="I68" s="15" t="inlineStr"/>
+      <c r="J68" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K68" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L68" s="15" t="n"/>
+      <c r="M68" s="15" t="n"/>
+      <c r="N68" s="17" t="inlineStr">
+        <is>
+          <t>NAME COLLISION - this clinic is already trading as 'Aleefy' in 6 October. Not a prospect first: check whether it is a trademark problem, or a partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>Animal Clinic</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr"/>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>0236852968</t>
+        </is>
+      </c>
+      <c r="G69" s="15" t="inlineStr"/>
+      <c r="H69" s="17" t="inlineStr"/>
+      <c r="I69" s="15" t="inlineStr"/>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K69" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L69" s="15" t="n"/>
+      <c r="M69" s="15" t="n"/>
+      <c r="N69" s="17" t="inlineStr">
+        <is>
+          <t>Landline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Benji Veterinary Centre</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr"/>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>01111207333</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>01111207333</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="inlineStr"/>
+      <c r="I70" s="15" t="inlineStr"/>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K70" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L70" s="15" t="n"/>
+      <c r="M70" s="15" t="n"/>
+      <c r="N70" s="17" t="inlineStr"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>Dajla Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr"/>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>01097337861</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr">
+        <is>
+          <t>01097337861</t>
+        </is>
+      </c>
+      <c r="H71" s="17" t="inlineStr"/>
+      <c r="I71" s="15" t="inlineStr"/>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K71" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L71" s="15" t="n"/>
+      <c r="M71" s="15" t="n"/>
+      <c r="N71" s="17" t="inlineStr"/>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Doctor Pets</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr"/>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>01064545446</t>
+        </is>
+      </c>
+      <c r="G72" s="16" t="inlineStr">
+        <is>
+          <t>01064545446</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr"/>
+      <c r="I72" s="15" t="inlineStr"/>
+      <c r="J72" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K72" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L72" s="15" t="n"/>
+      <c r="M72" s="15" t="n"/>
+      <c r="N72" s="17" t="inlineStr"/>
+    </row>
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>Domestic Vet Clinic</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr"/>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>01094974732</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="inlineStr">
+        <is>
+          <t>01094974732</t>
+        </is>
+      </c>
+      <c r="H73" s="17" t="inlineStr"/>
+      <c r="I73" s="15" t="inlineStr"/>
+      <c r="J73" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K73" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L73" s="15" t="n"/>
+      <c r="M73" s="15" t="n"/>
+      <c r="N73" s="17" t="inlineStr"/>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>Dr Howaida Ismail Clinic</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr"/>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>01116655514</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>01116655514</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr"/>
+      <c r="I74" s="15" t="inlineStr"/>
+      <c r="J74" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K74" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L74" s="15" t="n"/>
+      <c r="M74" s="15" t="n"/>
+      <c r="N74" s="17" t="inlineStr">
+        <is>
+          <t>Named after the vet - decision maker is on the sign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>Dr Khaled Ali</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr"/>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>01008233425</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>01008233425</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="inlineStr"/>
+      <c r="I75" s="15" t="inlineStr"/>
+      <c r="J75" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K75" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L75" s="15" t="n"/>
+      <c r="M75" s="15" t="n"/>
+      <c r="N75" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01111200798. Named after the vet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>Dr Raymond Nabih</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr"/>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>01221746549</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="inlineStr">
+        <is>
+          <t>01221746549</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr"/>
+      <c r="I76" s="15" t="inlineStr"/>
+      <c r="J76" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K76" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L76" s="15" t="n"/>
+      <c r="M76" s="15" t="n"/>
+      <c r="N76" s="17" t="inlineStr">
+        <is>
+          <t>Named after the vet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>Elite Blue Veterinary Center</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr"/>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F77" s="16" t="inlineStr">
+        <is>
+          <t>01020511166</t>
+        </is>
+      </c>
+      <c r="G77" s="16" t="inlineStr">
+        <is>
+          <t>01020511166</t>
+        </is>
+      </c>
+      <c r="H77" s="17" t="inlineStr"/>
+      <c r="I77" s="15" t="inlineStr"/>
+      <c r="J77" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K77" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L77" s="15" t="n"/>
+      <c r="M77" s="15" t="n"/>
+      <c r="N77" s="17" t="inlineStr"/>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Elite Veterinary Center</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="6" t="inlineStr"/>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>researchable</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="n"/>
+      <c r="M78" s="6" t="n"/>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>NO PHONE LISTED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>Enaya Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr"/>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F79" s="16" t="inlineStr">
+        <is>
+          <t>01062696178</t>
+        </is>
+      </c>
+      <c r="G79" s="16" t="inlineStr">
+        <is>
+          <t>01062696178</t>
+        </is>
+      </c>
+      <c r="H79" s="17" t="inlineStr"/>
+      <c r="I79" s="15" t="inlineStr"/>
+      <c r="J79" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K79" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L79" s="15" t="n"/>
+      <c r="M79" s="15" t="n"/>
+      <c r="N79" s="17" t="inlineStr"/>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Family Animal Care Center</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr"/>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>01005200319</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="inlineStr">
+        <is>
+          <t>01005200319</t>
+        </is>
+      </c>
+      <c r="H80" s="17" t="inlineStr"/>
+      <c r="I80" s="15" t="inlineStr"/>
+      <c r="J80" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L80" s="15" t="n"/>
+      <c r="M80" s="15" t="n"/>
+      <c r="N80" s="17" t="inlineStr"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B81" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>Fidge Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr"/>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F81" s="16" t="inlineStr">
+        <is>
+          <t>01065866066</t>
+        </is>
+      </c>
+      <c r="G81" s="16" t="inlineStr">
+        <is>
+          <t>01065866066</t>
+        </is>
+      </c>
+      <c r="H81" s="17" t="inlineStr"/>
+      <c r="I81" s="15" t="inlineStr"/>
+      <c r="J81" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L81" s="15" t="n"/>
+      <c r="M81" s="15" t="n"/>
+      <c r="N81" s="17" t="inlineStr"/>
+    </row>
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>Funny Pets</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr"/>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>01025688989</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>01025688989</t>
+        </is>
+      </c>
+      <c r="H82" s="17" t="inlineStr"/>
+      <c r="I82" s="15" t="inlineStr"/>
+      <c r="J82" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K82" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L82" s="15" t="n"/>
+      <c r="M82" s="15" t="n"/>
+      <c r="N82" s="17" t="inlineStr"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>Golden Fit Clinic</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr"/>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F83" s="16" t="inlineStr">
+        <is>
+          <t>01006244766</t>
+        </is>
+      </c>
+      <c r="G83" s="16" t="inlineStr">
+        <is>
+          <t>01006244766</t>
+        </is>
+      </c>
+      <c r="H83" s="17" t="inlineStr"/>
+      <c r="I83" s="15" t="inlineStr"/>
+      <c r="J83" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K83" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L83" s="15" t="n"/>
+      <c r="M83" s="15" t="n"/>
+      <c r="N83" s="17" t="inlineStr"/>
+    </row>
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>Loyal Friends Vet Clinic</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr"/>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>01007226786</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="inlineStr">
+        <is>
+          <t>01007226786</t>
+        </is>
+      </c>
+      <c r="H84" s="17" t="inlineStr"/>
+      <c r="I84" s="15" t="inlineStr"/>
+      <c r="J84" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K84" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L84" s="15" t="n"/>
+      <c r="M84" s="15" t="n"/>
+      <c r="N84" s="17" t="inlineStr">
+        <is>
+          <t>Surgery advertised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>October Clinics</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr"/>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F85" s="16" t="inlineStr">
+        <is>
+          <t>01101160644</t>
+        </is>
+      </c>
+      <c r="G85" s="16" t="inlineStr">
+        <is>
+          <t>01101160644</t>
+        </is>
+      </c>
+      <c r="H85" s="17" t="inlineStr"/>
+      <c r="I85" s="15" t="inlineStr"/>
+      <c r="J85" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K85" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L85" s="15" t="n"/>
+      <c r="M85" s="15" t="n"/>
+      <c r="N85" s="17" t="inlineStr">
+        <is>
+          <t>PLURAL name - ask whether there is more than one site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B86" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>October Vet Clinic</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr"/>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>01223578982</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>01223578982</t>
+        </is>
+      </c>
+      <c r="H86" s="17" t="inlineStr"/>
+      <c r="I86" s="15" t="inlineStr"/>
+      <c r="J86" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K86" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L86" s="15" t="n"/>
+      <c r="M86" s="15" t="n"/>
+      <c r="N86" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 0236976564.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>One O One Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr"/>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F87" s="16" t="inlineStr">
+        <is>
+          <t>01116111339</t>
+        </is>
+      </c>
+      <c r="G87" s="16" t="inlineStr">
+        <is>
+          <t>01116111339</t>
+        </is>
+      </c>
+      <c r="H87" s="17" t="inlineStr"/>
+      <c r="I87" s="15" t="inlineStr"/>
+      <c r="J87" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K87" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L87" s="15" t="n"/>
+      <c r="M87" s="15" t="n"/>
+      <c r="N87" s="17" t="inlineStr"/>
+    </row>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>Pawfect Vet Clinic</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr"/>
+      <c r="E88" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>01153104213</t>
+        </is>
+      </c>
+      <c r="G88" s="16" t="inlineStr">
+        <is>
+          <t>01153104213</t>
+        </is>
+      </c>
+      <c r="H88" s="17" t="inlineStr"/>
+      <c r="I88" s="15" t="inlineStr"/>
+      <c r="J88" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K88" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L88" s="15" t="n"/>
+      <c r="M88" s="15" t="n"/>
+      <c r="N88" s="17" t="inlineStr"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>Pet Animals Clinic</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr"/>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F89" s="16" t="inlineStr">
+        <is>
+          <t>01020099123</t>
+        </is>
+      </c>
+      <c r="G89" s="16" t="inlineStr">
+        <is>
+          <t>01020099123</t>
+        </is>
+      </c>
+      <c r="H89" s="17" t="inlineStr"/>
+      <c r="I89" s="15" t="inlineStr"/>
+      <c r="J89" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K89" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L89" s="15" t="n"/>
+      <c r="M89" s="15" t="n"/>
+      <c r="N89" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01020099188.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>Pet Life Clinic</t>
+        </is>
+      </c>
+      <c r="D90" s="15" t="inlineStr"/>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>01143853080</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>01143853080</t>
+        </is>
+      </c>
+      <c r="H90" s="17" t="inlineStr"/>
+      <c r="I90" s="15" t="inlineStr"/>
+      <c r="J90" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K90" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L90" s="15" t="n"/>
+      <c r="M90" s="15" t="n"/>
+      <c r="N90" s="17" t="inlineStr"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>Pet Lovers Clinic</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr"/>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F91" s="16" t="inlineStr">
+        <is>
+          <t>01221948424</t>
+        </is>
+      </c>
+      <c r="G91" s="16" t="inlineStr">
+        <is>
+          <t>01221948424</t>
+        </is>
+      </c>
+      <c r="H91" s="17" t="inlineStr"/>
+      <c r="I91" s="15" t="inlineStr"/>
+      <c r="J91" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K91" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L91" s="15" t="n"/>
+      <c r="M91" s="15" t="n"/>
+      <c r="N91" s="17" t="inlineStr"/>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>Pet Medic</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr"/>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F92" s="16" t="inlineStr">
+        <is>
+          <t>01117703421</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr">
+        <is>
+          <t>01117703421</t>
+        </is>
+      </c>
+      <c r="H92" s="17" t="inlineStr"/>
+      <c r="I92" s="15" t="inlineStr"/>
+      <c r="J92" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K92" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L92" s="15" t="n"/>
+      <c r="M92" s="15" t="n"/>
+      <c r="N92" s="17" t="inlineStr"/>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>Pets Care October</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr"/>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F93" s="16" t="inlineStr">
+        <is>
+          <t>01020076494</t>
+        </is>
+      </c>
+      <c r="G93" s="16" t="inlineStr">
+        <is>
+          <t>01020076494</t>
+        </is>
+      </c>
+      <c r="H93" s="17" t="inlineStr"/>
+      <c r="I93" s="15" t="inlineStr"/>
+      <c r="J93" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K93" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L93" s="15" t="n"/>
+      <c r="M93" s="15" t="n"/>
+      <c r="N93" s="17" t="inlineStr"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>Pets Cure Center</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr"/>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>01020495194</t>
+        </is>
+      </c>
+      <c r="G94" s="16" t="inlineStr">
+        <is>
+          <t>01020495194</t>
+        </is>
+      </c>
+      <c r="H94" s="17" t="inlineStr"/>
+      <c r="I94" s="15" t="inlineStr"/>
+      <c r="J94" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K94" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L94" s="15" t="n"/>
+      <c r="M94" s="15" t="n"/>
+      <c r="N94" s="17" t="inlineStr"/>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B95" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>Pets Home Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr"/>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F95" s="16" t="inlineStr">
+        <is>
+          <t>0101920883</t>
+        </is>
+      </c>
+      <c r="G95" s="16" t="inlineStr">
+        <is>
+          <t>0101920883</t>
+        </is>
+      </c>
+      <c r="H95" s="17" t="inlineStr"/>
+      <c r="I95" s="15" t="inlineStr"/>
+      <c r="J95" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K95" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L95" s="15" t="n"/>
+      <c r="M95" s="15" t="n"/>
+      <c r="N95" s="17" t="inlineStr"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>Pets and Pets</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr"/>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>01111120746</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="inlineStr">
+        <is>
+          <t>01111120746</t>
+        </is>
+      </c>
+      <c r="H96" s="17" t="inlineStr"/>
+      <c r="I96" s="15" t="inlineStr"/>
+      <c r="J96" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K96" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L96" s="15" t="n"/>
+      <c r="M96" s="15" t="n"/>
+      <c r="N96" s="17" t="inlineStr"/>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>Petsiano Clinic</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr"/>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F97" s="16" t="inlineStr">
+        <is>
+          <t>01002665934</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="inlineStr">
+        <is>
+          <t>01002665934</t>
+        </is>
+      </c>
+      <c r="H97" s="17" t="inlineStr"/>
+      <c r="I97" s="15" t="inlineStr"/>
+      <c r="J97" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K97" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L97" s="15" t="n"/>
+      <c r="M97" s="15" t="n"/>
+      <c r="N97" s="17" t="inlineStr"/>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>Polaris Pet Clinic</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr"/>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>01015915824</t>
+        </is>
+      </c>
+      <c r="G98" s="16" t="inlineStr">
+        <is>
+          <t>01015915824</t>
+        </is>
+      </c>
+      <c r="H98" s="17" t="inlineStr"/>
+      <c r="I98" s="15" t="inlineStr"/>
+      <c r="J98" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K98" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L98" s="15" t="n"/>
+      <c r="M98" s="15" t="n"/>
+      <c r="N98" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01014710710. Two lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B99" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>Pulse Veterinary Center</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr"/>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F99" s="16" t="inlineStr">
+        <is>
+          <t>01065376564</t>
+        </is>
+      </c>
+      <c r="G99" s="16" t="inlineStr">
+        <is>
+          <t>01065376564</t>
+        </is>
+      </c>
+      <c r="H99" s="17" t="inlineStr"/>
+      <c r="I99" s="15" t="inlineStr"/>
+      <c r="J99" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K99" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L99" s="15" t="n"/>
+      <c r="M99" s="15" t="n"/>
+      <c r="N99" s="17" t="inlineStr"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>Royals Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr"/>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F100" s="16" t="inlineStr">
+        <is>
+          <t>01158658258</t>
+        </is>
+      </c>
+      <c r="G100" s="16" t="inlineStr">
+        <is>
+          <t>01158658258</t>
+        </is>
+      </c>
+      <c r="H100" s="17" t="inlineStr"/>
+      <c r="I100" s="15" t="inlineStr"/>
+      <c r="J100" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K100" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L100" s="15" t="n"/>
+      <c r="M100" s="15" t="n"/>
+      <c r="N100" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01012499666.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B101" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>Sham Pets</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr"/>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F101" s="16" t="inlineStr">
+        <is>
+          <t>01066506665</t>
+        </is>
+      </c>
+      <c r="G101" s="16" t="inlineStr">
+        <is>
+          <t>01066506665</t>
+        </is>
+      </c>
+      <c r="H101" s="17" t="inlineStr"/>
+      <c r="I101" s="15" t="inlineStr"/>
+      <c r="J101" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K101" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L101" s="15" t="n"/>
+      <c r="M101" s="15" t="n"/>
+      <c r="N101" s="17" t="inlineStr"/>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>Sixth October Veterinary Services Center</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr"/>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>01229729713</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="inlineStr">
+        <is>
+          <t>01229729713</t>
+        </is>
+      </c>
+      <c r="H102" s="17" t="inlineStr"/>
+      <c r="I102" s="15" t="inlineStr"/>
+      <c r="J102" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K102" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L102" s="15" t="n"/>
+      <c r="M102" s="15" t="n"/>
+      <c r="N102" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01289009732. Two lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B103" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>Skyline Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="inlineStr"/>
+      <c r="E103" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F103" s="16" t="inlineStr">
+        <is>
+          <t>01149336393</t>
+        </is>
+      </c>
+      <c r="G103" s="16" t="inlineStr">
+        <is>
+          <t>01149336393</t>
+        </is>
+      </c>
+      <c r="H103" s="17" t="inlineStr"/>
+      <c r="I103" s="15" t="inlineStr"/>
+      <c r="J103" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K103" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L103" s="15" t="n"/>
+      <c r="M103" s="15" t="n"/>
+      <c r="N103" s="17" t="inlineStr"/>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B104" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>Smart Vet Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr"/>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>01147355699</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="inlineStr">
+        <is>
+          <t>01147355699</t>
+        </is>
+      </c>
+      <c r="H104" s="17" t="inlineStr"/>
+      <c r="I104" s="15" t="inlineStr"/>
+      <c r="J104" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K104" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L104" s="15" t="n"/>
+      <c r="M104" s="15" t="n"/>
+      <c r="N104" s="17" t="inlineStr"/>
+    </row>
+    <row r="105" ht="30" customHeight="1">
+      <c r="A105" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>VETMAN Veterinary Center</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="inlineStr"/>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="F105" s="16" t="inlineStr">
+        <is>
+          <t>01220872804</t>
+        </is>
+      </c>
+      <c r="G105" s="16" t="inlineStr">
+        <is>
+          <t>01220872804</t>
+        </is>
+      </c>
+      <c r="H105" s="17" t="inlineStr"/>
+      <c r="I105" s="15" t="inlineStr"/>
+      <c r="J105" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K105" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L105" s="15" t="n"/>
+      <c r="M105" s="15" t="n"/>
+      <c r="N105" s="17" t="inlineStr"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B106" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>Best 4 Pets Vet Clinic</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr"/>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>Giza</t>
+        </is>
+      </c>
+      <c r="F106" s="16" t="inlineStr">
+        <is>
+          <t>01202700118</t>
+        </is>
+      </c>
+      <c r="G106" s="16" t="inlineStr">
+        <is>
+          <t>01202700118</t>
+        </is>
+      </c>
+      <c r="H106" s="17" t="inlineStr"/>
+      <c r="I106" s="15" t="inlineStr"/>
+      <c r="J106" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K106" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L106" s="15" t="n"/>
+      <c r="M106" s="15" t="n"/>
+      <c r="N106" s="17" t="inlineStr"/>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>Prestige Animal Clinic</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="inlineStr"/>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>Haram</t>
+        </is>
+      </c>
+      <c r="F107" s="16" t="inlineStr">
+        <is>
+          <t>01223703448</t>
+        </is>
+      </c>
+      <c r="G107" s="16" t="inlineStr">
+        <is>
+          <t>01223703448</t>
+        </is>
+      </c>
+      <c r="H107" s="17" t="inlineStr"/>
+      <c r="I107" s="15" t="inlineStr"/>
+      <c r="J107" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K107" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L107" s="15" t="n"/>
+      <c r="M107" s="15" t="n"/>
+      <c r="N107" s="17" t="inlineStr"/>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>Vethouse Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr"/>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>Haram</t>
+        </is>
+      </c>
+      <c r="F108" s="16" t="inlineStr">
+        <is>
+          <t>01126885812</t>
+        </is>
+      </c>
+      <c r="G108" s="16" t="inlineStr">
+        <is>
+          <t>01126885812</t>
+        </is>
+      </c>
+      <c r="H108" s="17" t="inlineStr"/>
+      <c r="I108" s="15" t="inlineStr"/>
+      <c r="J108" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K108" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L108" s="15" t="n"/>
+      <c r="M108" s="15" t="n"/>
+      <c r="N108" s="17" t="inlineStr"/>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B109" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>Petzone Clinics - Mohandessin</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr"/>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="D109" s="10" t="inlineStr"/>
+      <c r="E109" s="10" t="inlineStr">
         <is>
           <t>Mohandessin</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="F109" s="11" t="inlineStr">
         <is>
           <t>01099975999</t>
         </is>
       </c>
-      <c r="G55" s="10" t="inlineStr"/>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="G109" s="10" t="inlineStr"/>
+      <c r="H109" s="12" t="inlineStr">
         <is>
           <t>3 branches · grooming · boarding · pharmacy · lab</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="I109" s="10" t="inlineStr"/>
+      <c r="J109" s="8" t="inlineStr">
         <is>
           <t>callable</t>
         </is>
       </c>
-      <c r="K55" s="10" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="L55" s="10" t="n"/>
-      <c r="M55" s="10" t="n"/>
-      <c r="N55" s="12" t="inlineStr">
+      <c r="K109" s="10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L109" s="10" t="n"/>
+      <c r="M109" s="10" t="n"/>
+      <c r="N109" s="12" t="inlineStr">
         <is>
           <t>BRANCH of Petzone - same decision maker as the New Cairo record. Do not pitch twice.</t>
         </is>
       </c>
     </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B110" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>Nabdh Alif Zayed Hospital 24hrs</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr"/>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F110" s="16" t="inlineStr">
+        <is>
+          <t>01026565923</t>
+        </is>
+      </c>
+      <c r="G110" s="16" t="inlineStr">
+        <is>
+          <t>01026565923</t>
+        </is>
+      </c>
+      <c r="H110" s="17" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="I110" s="15" t="inlineStr"/>
+      <c r="J110" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K110" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L110" s="15" t="n"/>
+      <c r="M110" s="15" t="n"/>
+      <c r="N110" s="17" t="inlineStr">
+        <is>
+          <t>HOSPITAL, 24 hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B111" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>Pet Care Hospital 24hrs</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="inlineStr"/>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F111" s="16" t="inlineStr">
+        <is>
+          <t>01004740482</t>
+        </is>
+      </c>
+      <c r="G111" s="16" t="inlineStr">
+        <is>
+          <t>01004740482</t>
+        </is>
+      </c>
+      <c r="H111" s="17" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="I111" s="15" t="inlineStr"/>
+      <c r="J111" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K111" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L111" s="15" t="n"/>
+      <c r="M111" s="15" t="n"/>
+      <c r="N111" s="17" t="inlineStr">
+        <is>
+          <t>HOSPITAL, 24 hours - a round-the-clock hospital runs shifts, which means rotas and handover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B112" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>Veterinario</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr"/>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F112" s="16" t="inlineStr">
+        <is>
+          <t>01101222345</t>
+        </is>
+      </c>
+      <c r="G112" s="16" t="inlineStr">
+        <is>
+          <t>01101222345</t>
+        </is>
+      </c>
+      <c r="H112" s="17" t="inlineStr">
+        <is>
+          <t>pharmacy</t>
+        </is>
+      </c>
+      <c r="I112" s="15" t="inlineStr"/>
+      <c r="J112" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K112" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L112" s="15" t="n"/>
+      <c r="M112" s="15" t="n"/>
+      <c r="N112" s="17" t="inlineStr">
+        <is>
+          <t>Pharmacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B113" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>Zayed Veterinary Hospital</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr"/>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F113" s="16" t="inlineStr">
+        <is>
+          <t>01004740482</t>
+        </is>
+      </c>
+      <c r="G113" s="16" t="inlineStr">
+        <is>
+          <t>01004740482</t>
+        </is>
+      </c>
+      <c r="H113" s="17" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="I113" s="15" t="inlineStr"/>
+      <c r="J113" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K113" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L113" s="15" t="n"/>
+      <c r="M113" s="15" t="n"/>
+      <c r="N113" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01092111110, 01140093913. HOSPITAL, three lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B114" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="14" t="inlineStr">
+        <is>
+          <t>Al-Wahda Veterinary Unit</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr"/>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F114" s="16" t="inlineStr">
+        <is>
+          <t>0235719284</t>
+        </is>
+      </c>
+      <c r="G114" s="15" t="inlineStr"/>
+      <c r="H114" s="17" t="inlineStr"/>
+      <c r="I114" s="15" t="inlineStr"/>
+      <c r="J114" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K114" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L114" s="15" t="n"/>
+      <c r="M114" s="15" t="n"/>
+      <c r="N114" s="17" t="inlineStr">
+        <is>
+          <t>Landline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B115" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>Beverly Vet Clinic</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="inlineStr"/>
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F115" s="16" t="inlineStr">
+        <is>
+          <t>01006875254</t>
+        </is>
+      </c>
+      <c r="G115" s="16" t="inlineStr">
+        <is>
+          <t>01006875254</t>
+        </is>
+      </c>
+      <c r="H115" s="17" t="inlineStr"/>
+      <c r="I115" s="15" t="inlineStr"/>
+      <c r="J115" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K115" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L115" s="15" t="n"/>
+      <c r="M115" s="15" t="n"/>
+      <c r="N115" s="17" t="inlineStr"/>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B116" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>C&amp;D Vet Clinic</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr"/>
+      <c r="E116" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F116" s="16" t="inlineStr">
+        <is>
+          <t>01144990226</t>
+        </is>
+      </c>
+      <c r="G116" s="16" t="inlineStr">
+        <is>
+          <t>01144990226</t>
+        </is>
+      </c>
+      <c r="H116" s="17" t="inlineStr"/>
+      <c r="I116" s="15" t="inlineStr"/>
+      <c r="J116" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K116" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L116" s="15" t="n"/>
+      <c r="M116" s="15" t="n"/>
+      <c r="N116" s="17" t="inlineStr"/>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B117" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>Dr Ameema Abdel Fattah</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="inlineStr"/>
+      <c r="E117" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F117" s="16" t="inlineStr">
+        <is>
+          <t>01065175553</t>
+        </is>
+      </c>
+      <c r="G117" s="16" t="inlineStr">
+        <is>
+          <t>01065175553</t>
+        </is>
+      </c>
+      <c r="H117" s="17" t="inlineStr"/>
+      <c r="I117" s="15" t="inlineStr"/>
+      <c r="J117" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K117" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L117" s="15" t="n"/>
+      <c r="M117" s="15" t="n"/>
+      <c r="N117" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 0238519975. Named after the vet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B118" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>Dr Nevin Hassan Hemad</t>
+        </is>
+      </c>
+      <c r="D118" s="15" t="inlineStr"/>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F118" s="16" t="inlineStr">
+        <is>
+          <t>01000487985</t>
+        </is>
+      </c>
+      <c r="G118" s="16" t="inlineStr">
+        <is>
+          <t>01000487985</t>
+        </is>
+      </c>
+      <c r="H118" s="17" t="inlineStr"/>
+      <c r="I118" s="15" t="inlineStr"/>
+      <c r="J118" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K118" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L118" s="15" t="n"/>
+      <c r="M118" s="15" t="n"/>
+      <c r="N118" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01123377186. Named after the vet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>Just Pets Clinic</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr"/>
+      <c r="E119" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F119" s="16" t="inlineStr">
+        <is>
+          <t>01016165165</t>
+        </is>
+      </c>
+      <c r="G119" s="16" t="inlineStr">
+        <is>
+          <t>01016165165</t>
+        </is>
+      </c>
+      <c r="H119" s="17" t="inlineStr"/>
+      <c r="I119" s="15" t="inlineStr"/>
+      <c r="J119" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K119" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L119" s="15" t="n"/>
+      <c r="M119" s="15" t="n"/>
+      <c r="N119" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01151515118. Two lines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="30" customHeight="1">
+      <c r="A120" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>Khufu Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr"/>
+      <c r="E120" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F120" s="16" t="inlineStr">
+        <is>
+          <t>01285592995</t>
+        </is>
+      </c>
+      <c r="G120" s="16" t="inlineStr">
+        <is>
+          <t>01285592995</t>
+        </is>
+      </c>
+      <c r="H120" s="17" t="inlineStr"/>
+      <c r="I120" s="15" t="inlineStr"/>
+      <c r="J120" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K120" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L120" s="15" t="n"/>
+      <c r="M120" s="15" t="n"/>
+      <c r="N120" s="17" t="inlineStr"/>
+    </row>
+    <row r="121" ht="30" customHeight="1">
+      <c r="A121" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>Pet's Story Clinic</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr"/>
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F121" s="16" t="inlineStr">
+        <is>
+          <t>01152279787</t>
+        </is>
+      </c>
+      <c r="G121" s="16" t="inlineStr">
+        <is>
+          <t>01152279787</t>
+        </is>
+      </c>
+      <c r="H121" s="17" t="inlineStr"/>
+      <c r="I121" s="15" t="inlineStr"/>
+      <c r="J121" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K121" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L121" s="15" t="n"/>
+      <c r="M121" s="15" t="n"/>
+      <c r="N121" s="17" t="inlineStr"/>
+    </row>
+    <row r="122" ht="30" customHeight="1">
+      <c r="A122" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>Pets Island Vet Center</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="inlineStr"/>
+      <c r="E122" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F122" s="16" t="inlineStr">
+        <is>
+          <t>01011772198</t>
+        </is>
+      </c>
+      <c r="G122" s="16" t="inlineStr">
+        <is>
+          <t>01011772198</t>
+        </is>
+      </c>
+      <c r="H122" s="17" t="inlineStr"/>
+      <c r="I122" s="15" t="inlineStr"/>
+      <c r="J122" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K122" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L122" s="15" t="n"/>
+      <c r="M122" s="15" t="n"/>
+      <c r="N122" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01014710710, 01018566654. THREE lines - usually a busy practice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="30" customHeight="1">
+      <c r="A123" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B123" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>Zayed Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr"/>
+      <c r="E123" s="15" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="F123" s="16" t="inlineStr">
+        <is>
+          <t>01014872687</t>
+        </is>
+      </c>
+      <c r="G123" s="16" t="inlineStr">
+        <is>
+          <t>01014872687</t>
+        </is>
+      </c>
+      <c r="H123" s="17" t="inlineStr"/>
+      <c r="I123" s="15" t="inlineStr"/>
+      <c r="J123" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K123" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L123" s="15" t="n"/>
+      <c r="M123" s="15" t="n"/>
+      <c r="N123" s="17" t="inlineStr"/>
+    </row>
+    <row r="124" ht="30" customHeight="1">
+      <c r="A124" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B124" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="14" t="inlineStr">
+        <is>
+          <t>Dr Yasser Hassan Abu Saada</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr"/>
+      <c r="E124" s="15" t="inlineStr">
+        <is>
+          <t>Shubramant</t>
+        </is>
+      </c>
+      <c r="F124" s="16" t="inlineStr">
+        <is>
+          <t>0233631275</t>
+        </is>
+      </c>
+      <c r="G124" s="15" t="inlineStr"/>
+      <c r="H124" s="17" t="inlineStr"/>
+      <c r="I124" s="15" t="inlineStr"/>
+      <c r="J124" s="13" t="inlineStr">
+        <is>
+          <t>callable</t>
+        </is>
+      </c>
+      <c r="K124" s="15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L124" s="15" t="n"/>
+      <c r="M124" s="15" t="n"/>
+      <c r="N124" s="17" t="inlineStr">
+        <is>
+          <t>Other lines: 01227409723. Named after the vet.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:N55"/>
+  <autoFilter ref="A4:N124"/>
   <mergeCells count="1">
     <mergeCell ref="A2:N2"/>
   </mergeCells>
@@ -3026,6 +6254,139 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F73" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F74" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F75" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F76" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F77" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F79" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F80" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F81" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F82" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F83" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F84" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F85" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F87" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F90" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F91" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F92" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F111" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F112" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F113" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F114" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F115" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F116" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F117" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F118" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F119" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F120" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F121" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F122" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F123" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F124" r:id="rId156"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3037,7 +6398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3053,75 +6414,75 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Clinics mapped</t>
         </is>
       </c>
-      <c r="B3" s="19" t="n">
-        <v>51</v>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="B3" s="24" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>every one carries the URL its facts came from</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Callable today</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="B4" s="24" t="n">
+        <v>84</v>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>a phone or WhatsApp number is on file</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Need a number</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="B5" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>an address or Facebook page but no phone - minutes each to find</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Score 8 or more</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>multi-branch or full-service: the clinics Aleefy's breadth is FOR</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Already on a competitor</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>willingness to pay is proven, and a contract is in the way</t>
         </is>
@@ -3135,202 +6496,267 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>District</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Clinics</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Callable</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>6 October</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>51</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Sheikh Zayed</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" s="27" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Heliopolis</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B13" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C13" s="27" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Nasr City</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B14" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C14" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>New Cairo</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B15" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C15" s="27" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Maadi</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
+      <c r="B16" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C16" s="27" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>(not recorded)</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
+      <c r="B17" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C17" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>New Maadi</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B18" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C18" s="27" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Nozha</t>
         </is>
       </c>
-      <c r="B17" s="22" t="n">
+      <c r="B19" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C19" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Haram</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Badr City</t>
         </is>
       </c>
-      <c r="B18" s="22" t="n">
+      <c r="B21" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="22" t="n">
+      <c r="C21" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Katameya</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n">
+      <c r="B22" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C22" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Obour</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B23" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="22" t="n">
+      <c r="C23" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Shorouk</t>
         </is>
       </c>
-      <c r="B21" s="22" t="n">
+      <c r="B24" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C24" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Zahraa El Maadi</t>
         </is>
       </c>
-      <c r="B22" s="22" t="n">
+      <c r="B25" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="22" t="n">
+      <c r="C25" s="27" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>Giza</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Mohandessin</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
+      <c r="B27" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C27" s="27" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>Shubramant</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Work one district at a time. Density is the mechanism - the goal is a vet saying 'I know several clinics using it', which never happens from one clinic per area.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
+    <row r="31"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A25:C26"/>
+    <mergeCell ref="A30:C31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3342,7 +6768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3358,893 +6784,2066 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>A market database nobody can audit is a list of rumours, and the first wrong phone number destroys trust in all of it.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Clinic</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C4" s="21" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>American Vet Center</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>https://www.americanvetcenter.com/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>British Animal Hospital</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>search result</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>http://britishanimalhospital.com/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Dr Men3am Pet Hospital</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>competitor research</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>https://veticareapp.com/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Almotawakkel Pet Center</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>competitor research</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>https://veticareapp.com/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Pets Zone</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>competitor research</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>https://veticareapp.com/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Biofy Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Petzone Clinics - Heliopolis</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>https://petzoneclinics.com/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Golf Veterinary Clinic Heliopolis</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Heliopolis Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Pet Vet Clinic</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Pets Galaxy</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Pets Home</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Pets Valley</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Vital Pets Center</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Dr Birjy Yaqoub Clinic</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Sheraton Vet Clinic</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>International Veterinary Hospital</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Dr Sameh Nabil Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>Arabic directory</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Golf Veterinary Clinic Maadi</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>Arabic directory</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>I-Vet Clinic</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Maadi Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>https://eg.daleel.waseet.net/en/cairo/</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Mojo Veterinary Care</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>competitor research</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>https://veticareapp.com/</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Pawsitive Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>Animalz</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Lovely Pets Clinic</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>Pet Hotel Nasr City</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Happy Pets</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>PWC Veterinary Center</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>Pet Care Center</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Pets Care Clinic</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>Pets Steps</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>VIPets Clinic</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/مدينة-نصر/</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>Dr Paws Animal Hospital</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="27" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>https://drpaws.com.eg/en/</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>Petzone Clinics</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>https://petzoneclinics.com/</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t>VENN Animal Hospital</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>https://vennvet.com/</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Pet Cure Veterinary Clinics</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
+      <c r="B40" s="27" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>https://petcureclinics.com/about-us</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="22" t="inlineStr">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>Lotus Veterinary Hospital</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr">
+      <c r="B41" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>Pet Hotel New Cairo</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B42" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="28" t="inlineStr">
         <is>
           <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>Pet Palace</t>
         </is>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B43" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="22" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>Pet Republic</t>
         </is>
       </c>
-      <c r="B44" s="22" t="inlineStr">
+      <c r="B44" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C44" s="23" t="inlineStr">
+      <c r="C44" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>Vetology Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B45" s="22" t="inlineStr">
+      <c r="B45" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>Pharma Vet</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
+      <c r="B46" s="27" t="inlineStr">
         <is>
           <t>Arabic directory</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="28" t="inlineStr">
         <is>
           <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>New Maadi Vet Clinic</t>
         </is>
       </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="B47" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>New York Veterinary Clinics</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="27" t="inlineStr">
         <is>
           <t>Arabic directory</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
+      <c r="C48" s="28" t="inlineStr">
         <is>
           <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="22" t="inlineStr">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>Paws &amp; Claws Vet Clinic</t>
         </is>
       </c>
-      <c r="B49" s="22" t="inlineStr">
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>directory</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="28" t="inlineStr">
         <is>
           <t>https://cairoscene.com/LifeStyle/Best-Vet-Clinics-in-Cairo</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>Harmony Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B50" s="22" t="inlineStr">
+      <c r="B50" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="28" t="inlineStr">
         <is>
           <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>El-Nozha Veterinary</t>
         </is>
       </c>
-      <c r="B51" s="22" t="inlineStr">
+      <c r="B51" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
+      <c r="C51" s="28" t="inlineStr">
         <is>
           <t>https://www.evcindex.com/loc/مصر-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="22" t="inlineStr">
+      <c r="A52" s="27" t="inlineStr">
         <is>
           <t>Paws and Claws Veterinary Clinic - Obour</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B52" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="inlineStr">
+      <c r="A53" s="27" t="inlineStr">
         <is>
           <t>Prime Vet Clinic</t>
         </is>
       </c>
-      <c r="B53" s="22" t="inlineStr">
+      <c r="B53" s="27" t="inlineStr">
         <is>
           <t>evcindex directory</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="28" t="inlineStr">
         <is>
           <t>http://www.evcindex.com/loc/القاهرة-الجديدة/</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>Nile Veterinary Clinic</t>
         </is>
       </c>
-      <c r="B54" s="22" t="inlineStr">
+      <c r="B54" s="27" t="inlineStr">
         <is>
           <t>Arabic directory</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="C54" s="28" t="inlineStr">
         <is>
           <t>https://dr.alyahmed.com/2022/02/blog-post_9.html</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>Pets Mall Hospital</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>Almedan Pet Hospital October</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>Catdog Hospital</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>Fardous Pets Clinics</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>Pets Place Clinic</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C59" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>Pets Planet Clinic</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C60" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>Very Important Pets</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>Vet4u</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>Veterinary Pharmacy October</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>Vito Vet</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>3naya Pet Clinic</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>6 October Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>Al-Siyaha Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>Aleefy Veterinary Center</t>
+        </is>
+      </c>
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>Animal Clinic</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C69" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="27" t="inlineStr">
+        <is>
+          <t>Benji Veterinary Centre</t>
+        </is>
+      </c>
+      <c r="B70" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>Dajla Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B71" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C71" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>Doctor Pets</t>
+        </is>
+      </c>
+      <c r="B72" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C72" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>Domestic Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>Dr Howaida Ismail Clinic</t>
+        </is>
+      </c>
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>Dr Khaled Ali</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>Dr Raymond Nabih</t>
+        </is>
+      </c>
+      <c r="B76" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C76" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>Elite Blue Veterinary Center</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C77" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="27" t="inlineStr">
+        <is>
+          <t>Elite Veterinary Center</t>
+        </is>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C78" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>Enaya Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C79" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="27" t="inlineStr">
+        <is>
+          <t>Family Animal Care Center</t>
+        </is>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C80" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>Fidge Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C81" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="27" t="inlineStr">
+        <is>
+          <t>Funny Pets</t>
+        </is>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C82" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>Golden Fit Clinic</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C83" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="27" t="inlineStr">
+        <is>
+          <t>Loyal Friends Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C84" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>October Clinics</t>
+        </is>
+      </c>
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C85" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="27" t="inlineStr">
+        <is>
+          <t>October Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C86" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>One O One Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C87" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="27" t="inlineStr">
+        <is>
+          <t>Pawfect Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C88" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>Pet Animals Clinic</t>
+        </is>
+      </c>
+      <c r="B89" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C89" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="27" t="inlineStr">
+        <is>
+          <t>Pet Life Clinic</t>
+        </is>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C90" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>Pet Lovers Clinic</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C91" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="27" t="inlineStr">
+        <is>
+          <t>Pet Medic</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C92" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>Pets Care October</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C93" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="27" t="inlineStr">
+        <is>
+          <t>Pets Cure Center</t>
+        </is>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C94" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>Pets Home Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C95" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="27" t="inlineStr">
+        <is>
+          <t>Pets and Pets</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C96" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>Petsiano Clinic</t>
+        </is>
+      </c>
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C97" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="27" t="inlineStr">
+        <is>
+          <t>Polaris Pet Clinic</t>
+        </is>
+      </c>
+      <c r="B98" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C98" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="27" t="inlineStr">
+        <is>
+          <t>Pulse Veterinary Center</t>
+        </is>
+      </c>
+      <c r="B99" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C99" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="27" t="inlineStr">
+        <is>
+          <t>Royals Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C100" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>Sham Pets</t>
+        </is>
+      </c>
+      <c r="B101" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C101" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="27" t="inlineStr">
+        <is>
+          <t>Sixth October Veterinary Services Center</t>
+        </is>
+      </c>
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C102" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="27" t="inlineStr">
+        <is>
+          <t>Skyline Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C103" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="27" t="inlineStr">
+        <is>
+          <t>Smart Vet Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B104" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C104" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>VETMAN Veterinary Center</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C105" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="27" t="inlineStr">
+        <is>
+          <t>Best 4 Pets Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B106" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C106" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>Prestige Animal Clinic</t>
+        </is>
+      </c>
+      <c r="B107" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C107" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="27" t="inlineStr">
+        <is>
+          <t>Vethouse Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C108" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="27" t="inlineStr">
         <is>
           <t>Petzone Clinics - Mohandessin</t>
         </is>
       </c>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B109" s="27" t="inlineStr">
         <is>
           <t>vendor site</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C109" s="28" t="inlineStr">
         <is>
           <t>https://petzoneclinics.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="27" t="inlineStr">
+        <is>
+          <t>Nabdh Alif Zayed Hospital 24hrs</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C110" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t>Pet Care Hospital 24hrs</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C111" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="27" t="inlineStr">
+        <is>
+          <t>Veterinario</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C112" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>Zayed Veterinary Hospital</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C113" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="27" t="inlineStr">
+        <is>
+          <t>Al-Wahda Veterinary Unit</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>Beverly Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C115" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="27" t="inlineStr">
+        <is>
+          <t>C&amp;D Vet Clinic</t>
+        </is>
+      </c>
+      <c r="B116" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C116" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="27" t="inlineStr">
+        <is>
+          <t>Dr Ameema Abdel Fattah</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C117" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="27" t="inlineStr">
+        <is>
+          <t>Dr Nevin Hassan Hemad</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C118" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>Just Pets Clinic</t>
+        </is>
+      </c>
+      <c r="B119" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C119" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="27" t="inlineStr">
+        <is>
+          <t>Khufu Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B120" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C120" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="27" t="inlineStr">
+        <is>
+          <t>Pet's Story Clinic</t>
+        </is>
+      </c>
+      <c r="B121" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C121" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="27" t="inlineStr">
+        <is>
+          <t>Pets Island Vet Center</t>
+        </is>
+      </c>
+      <c r="B122" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C122" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="27" t="inlineStr">
+        <is>
+          <t>Zayed Veterinary Clinic</t>
+        </is>
+      </c>
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="27" t="inlineStr">
+        <is>
+          <t>Dr Yasser Hassan Abu Saada</t>
+        </is>
+      </c>
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>to-all.com directory</t>
+        </is>
+      </c>
+      <c r="C124" s="28" t="inlineStr">
+        <is>
+          <t>https://www.to-all.com/veterinary-october/</t>
         </is>
       </c>
     </row>
@@ -4301,6 +8900,75 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
